--- a/sequences/retrieval_blockA_fixed-middle-10_16.xlsx
+++ b/sequences/retrieval_blockA_fixed-middle-10_16.xlsx
@@ -562,22 +562,22 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>stimuli/house/house_02.jpg</t>
+          <t>stimuli/bicycle/bicycle_39.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>stimuli/jacket/jacket_19.jpg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>stimuli/house/house_02.jpg</t>
+          <t>stimuli/bicycle/bicycle_39.jpg</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>stimuli/jacket/jacket_19.jpg</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
         <v>1.5</v>
@@ -612,15 +612,15 @@
         <v>7</v>
       </c>
       <c r="T2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -645,18 +645,22 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_19.jpg</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>stimuli/chair/chair_21.jpg</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>stimuli/ball/ball_33.jpg</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -670,32 +674,36 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>6</v>
+      </c>
       <c r="P3" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="Q3" t="n">
         <v>0.2</v>
       </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
         <v>5</v>
       </c>
       <c r="T3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -715,65 +723,43 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_18.jpg</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>stimuli/house/house_02.jpg</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_18.jpg</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_18.jpg</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
-      <c r="O4" t="n">
-        <v>8</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="n">
         <v>9</v>
       </c>
-      <c r="T4" t="n">
-        <v>8</v>
-      </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -798,12 +784,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/flower/flower_28.jpg</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_18.jpg</t>
+          <t>stimuli/bicycle/bicycle_39.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -819,16 +805,16 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -839,13 +825,13 @@
         <v>0.2</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -853,7 +839,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -873,7 +859,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_28.jpg</t>
+          <t>stimuli/hand/hand_18.jpg</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -882,28 +868,42 @@
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R6" t="inlineStr"/>
+        <v>0.2</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T6" t="n">
         <v>4</v>
@@ -914,7 +914,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -934,40 +934,54 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_12.jpg</t>
+          <t>stimuli/jacket/jacket_19.jpg</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>stimuli/flower/flower_28.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R7" t="inlineStr"/>
+        <v>0.2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -975,7 +989,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -995,23 +1009,27 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_28.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>stimuli/hammer/hammer_12.jpg</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/hammer/hammer_12.jpg</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1025,27 +1043,31 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>4</v>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>3</v>
+      </c>
       <c r="P8" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="Q8" t="n">
         <v>0.2</v>
       </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
+        <v>7</v>
+      </c>
+      <c r="U8" t="n">
         <v>4</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1075,7 +1097,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
+          <t>stimuli/flower/flower_28.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -1100,7 +1122,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -1117,7 +1139,7 @@
         <v>9</v>
       </c>
       <c r="T9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1145,29 +1167,29 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_18.jpg</t>
+          <t>stimuli/hammer/hammer_12.jpg</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>stimuli/hand/hand_18.jpg</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_15.jpg</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>stimuli/hand/hand_18.jpg</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_15.jpg</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>left</t>
@@ -1179,7 +1201,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1187,7 +1209,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
         <v>1.5</v>
@@ -1197,18 +1219,18 @@
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1228,65 +1250,43 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_19.jpg</t>
+          <t>stimuli/flower/flower_28.jpg</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_15.jpg</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_18.jpg</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_15.jpg</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_18.jpg</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
+          <t>stimuli/bicycle/bicycle_39.jpg</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>inside</t>
-        </is>
-      </c>
-      <c r="O11" t="n">
-        <v>4</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
+          <t>stimuli/dog/dog_15.jpg</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1332,16 +1332,16 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         <v>0.2</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_15.jpg</t>
+          <t>stimuli/hammer/hammer_12.jpg</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_12.jpg</t>
+          <t>stimuli/jacket/jacket_19.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -1400,11 +1400,11 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -1416,10 +1416,10 @@
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1427,7 +1427,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1447,23 +1447,27 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>stimuli/hand/hand_18.jpg</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_18.jpg</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>stimuli/dog/dog_15.jpg</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/dog/dog_15.jpg</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1477,32 +1481,36 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>3</v>
+      </c>
       <c r="P14" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="Q14" t="n">
         <v>0.2</v>
       </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
+      <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
+        <v>8</v>
+      </c>
+      <c r="T14" t="n">
         <v>4</v>
       </c>
-      <c r="T14" t="n">
-        <v>3</v>
-      </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1522,27 +1530,23 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_28.jpg</t>
+          <t>stimuli/house/house_02.jpg</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>stimuli/house/house_02.jpg</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
           <t>stimuli/bread/bread_18.jpg</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>stimuli/house/house_02.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_18.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1556,31 +1560,27 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>inside</t>
-        </is>
-      </c>
-      <c r="O15" t="n">
-        <v>6</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="Q15" t="n">
         <v>0.2</v>
       </c>
-      <c r="R15" t="inlineStr"/>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T15" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1605,27 +1605,27 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>stimuli/bicycle/bicycle_39.jpg</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_19.jpg</t>
+          <t>stimuli/flower/flower_28.jpg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_19.jpg</t>
+          <t>stimuli/flower/flower_28.jpg</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1657,18 +1657,18 @@
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1688,23 +1688,27 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>stimuli/bread/bread_18.jpg</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>stimuli/dog/dog_15.jpg</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/bread/bread_18.jpg</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/dog/dog_15.jpg</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1718,32 +1722,36 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>6</v>
+      </c>
       <c r="P17" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="Q17" t="n">
         <v>0.2</v>
       </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
+      <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1763,70 +1771,62 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_12.jpg</t>
+          <t>stimuli/jacket/jacket_19.jpg</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_15.jpg</t>
-        </is>
-      </c>
+          <t>stimuli/bicycle/bicycle_39.jpg</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_15.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>2</v>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>inside</t>
-        </is>
-      </c>
-      <c r="O18" t="n">
-        <v>3</v>
-      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="Q18" t="n">
         <v>0.2</v>
       </c>
-      <c r="R18" t="inlineStr"/>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T18" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1846,48 +1846,70 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>stimuli/house/house_02.jpg</t>
+          <t>stimuli/flower/flower_28.jpg</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_28.jpg</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+          <t>stimuli/chair/chair_21.jpg</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>stimuli/hammer/hammer_12.jpg</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>stimuli/chair/chair_21.jpg</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stimuli/hammer/hammer_12.jpg</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>3</v>
+      </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1907,70 +1929,62 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_18.jpg</t>
+          <t>stimuli/hand/hand_18.jpg</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
-        </is>
-      </c>
+          <t>stimuli/house/house_02.jpg</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
-      <c r="O20" t="n">
-        <v>4</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="Q20" t="n">
         <v>0.2</v>
       </c>
-      <c r="R20" t="inlineStr"/>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T20" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="U20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1990,33 +2004,21 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_19.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>stimuli/dog/dog_15.jpg</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M21" t="n">
@@ -2025,19 +2027,17 @@
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -2070,7 +2070,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_18.jpg</t>
+          <t>stimuli/flower/flower_28.jpg</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -2086,16 +2086,16 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
@@ -2106,13 +2106,13 @@
         <v>0.2</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>7</v>
       </c>
       <c r="T22" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -2120,7 +2120,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2140,54 +2140,40 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_15.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
+          <t>stimuli/hand/hand_18.jpg</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="R23" t="inlineStr"/>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -2215,27 +2201,27 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_18.jpg</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>stimuli/bicycle/bicycle_39.jpg</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
           <t>stimuli/jacket/jacket_19.jpg</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_18.jpg</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_02.jpg</t>
-        </is>
-      </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>stimuli/bicycle/bicycle_39.jpg</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>stimuli/house/house_02.jpg</t>
+          <t>stimuli/jacket/jacket_19.jpg</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2253,11 +2239,11 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>inside</t>
+          <t>outside</t>
         </is>
       </c>
       <c r="O24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P24" t="n">
         <v>1.5</v>
@@ -2267,18 +2253,18 @@
       </c>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="n">
+        <v>3</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
         <v>10</v>
-      </c>
-      <c r="T24" t="n">
-        <v>8</v>
-      </c>
-      <c r="U24" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2307,26 +2293,40 @@
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R25" t="inlineStr"/>
+        <v>0.2</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
       <c r="S25" t="n">
         <v>1</v>
       </c>
@@ -2359,37 +2359,37 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_28.jpg</t>
+          <t>stimuli/bread/bread_18.jpg</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/bicycle/bicycle_39.jpg</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/hammer/hammer_12.jpg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/bicycle/bicycle_39.jpg</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/hammer/hammer_12.jpg</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M26" t="n">
@@ -2401,7 +2401,7 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P26" t="n">
         <v>1.5</v>
@@ -2411,18 +2411,18 @@
       </c>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2450,49 +2450,41 @@
           <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_18.jpg</t>
-        </is>
-      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_18.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>4</v>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
-      <c r="O27" t="n">
-        <v>6</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
       <c r="P27" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="Q27" t="n">
         <v>0.2</v>
       </c>
-      <c r="R27" t="inlineStr"/>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
       <c r="S27" t="n">
         <v>6</v>
       </c>
@@ -2500,7 +2492,7 @@
         <v>4</v>
       </c>
       <c r="U27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2525,12 +2517,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_19.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>stimuli/hammer/hammer_12.jpg</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2540,7 +2532,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>stimuli/hammer/hammer_12.jpg</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2559,15 +2551,15 @@
         </is>
       </c>
       <c r="M28" t="n">
+        <v>2</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
         <v>3</v>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>inside</t>
-        </is>
-      </c>
-      <c r="O28" t="n">
-        <v>4</v>
       </c>
       <c r="P28" t="n">
         <v>1.5</v>
@@ -2577,10 +2569,10 @@
       </c>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U28" t="n">
         <v>9</v>
@@ -2588,7 +2580,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2608,21 +2600,33 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_39.jpg</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_15.jpg</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
-        </is>
-      </c>
       <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M29" t="n">
@@ -2631,17 +2635,19 @@
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R29" t="inlineStr"/>
+        <v>0.2</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
       <c r="S29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T29" t="n">
         <v>5</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -2649,7 +2655,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2669,33 +2675,21 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/hand/hand_18.jpg</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>stimuli/jacket/jacket_19.jpg</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M30" t="n">
@@ -2704,19 +2698,17 @@
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -2724,7 +2716,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -2752,15 +2744,19 @@
           <t>stimuli/bread/bread_18.jpg</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>stimuli/chair/chair_21.jpg</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/bread/bread_18.jpg</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2774,19 +2770,23 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>2</v>
-      </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
+        <v>5</v>
+      </c>
       <c r="P31" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="Q31" t="n">
         <v>0.2</v>
       </c>
-      <c r="R31" t="n">
-        <v>1</v>
-      </c>
+      <c r="R31" t="inlineStr"/>
       <c r="S31" t="n">
         <v>7</v>
       </c>
@@ -2794,7 +2794,7 @@
         <v>3</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/sequences/retrieval_blockA_fixed-middle-10_16.xlsx
+++ b/sequences/retrieval_blockA_fixed-middle-10_16.xlsx
@@ -491,32 +491,32 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>is_yes</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>distance_correct</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>type2_anchor_pos</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>dist_anchor_to_foil</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>image_dur_retr</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>fix_dur_retr</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>is_yes</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
@@ -537,7 +537,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -557,27 +557,23 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_12.jpg</t>
+          <t>stimuli/hand/hand_18.jpg</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_19.jpg</t>
-        </is>
-      </c>
+          <t>stimuli/house/house_02.jpg</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_19.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -593,29 +589,25 @@
       <c r="M2" t="n">
         <v>0</v>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>inside</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.5</v>
-      </c>
+      <c r="N2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R2" t="n">
         <v>0.2</v>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="U2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -640,27 +632,27 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_15.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/hammer/hammer_12.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/jacket/jacket_19.jpg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/hammer/hammer_12.jpg</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/jacket/jacket_19.jpg</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -673,37 +665,37 @@
           <t>right</t>
         </is>
       </c>
-      <c r="M3" t="n">
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="n">
         <v>4</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>outside</t>
         </is>
       </c>
-      <c r="O3" t="n">
-        <v>6</v>
-      </c>
       <c r="P3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q3" t="n">
         <v>1.5</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>0.2</v>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -723,40 +715,54 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_18.jpg</t>
+          <t>stimuli/house/house_02.jpg</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>stimuli/house/house_02.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>1</v>
       </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>2</v>
+      </c>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="n">
-        <v>2</v>
-      </c>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R4" t="inlineStr"/>
+        <v>1.2</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.2</v>
+      </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -764,7 +770,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -784,54 +790,40 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_28.jpg</t>
+          <t>stimuli/jacket/jacket_19.jpg</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
+          <t>stimuli/hand/hand_18.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>3</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
       <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>1.2</v>
-      </c>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -839,7 +831,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -859,62 +851,70 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>stimuli/house/house_02.jpg</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>stimuli/flower/flower_28.jpg</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/house/house_02.jpg</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/flower/flower_28.jpg</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>2</v>
-      </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
       <c r="P6" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="Q6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R6" t="n">
         <v>0.2</v>
       </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -934,23 +934,27 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>stimuli/ball/ball_33.jpg</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>stimuli/hammer/hammer_12.jpg</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>stimuli/jacket/jacket_19.jpg</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_28.jpg</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/hammer/hammer_12.jpg</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/jacket/jacket_19.jpg</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -963,33 +967,37 @@
           <t>right</t>
         </is>
       </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>2</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
       <c r="P7" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R7" t="n">
         <v>0.2</v>
       </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
       <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>7</v>
+      </c>
+      <c r="U7" t="n">
         <v>10</v>
-      </c>
-      <c r="T7" t="n">
-        <v>6</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1009,70 +1017,48 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/flower/flower_28.jpg</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_12.jpg</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_21.jpg</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_12.jpg</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_21.jpg</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
+          <t>stimuli/bicycle/bicycle_39.jpg</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>inside</t>
-        </is>
-      </c>
-      <c r="O8" t="n">
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="n">
         <v>3</v>
       </c>
-      <c r="P8" t="n">
-        <v>1.5</v>
-      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R8" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.5</v>
+      </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1092,23 +1078,27 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>stimuli/house/house_02.jpg</t>
+          <t>stimuli/jacket/jacket_19.jpg</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_28.jpg</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>stimuli/dog/dog_15.jpg</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>stimuli/chair/chair_21.jpg</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/dog/dog_15.jpg</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1121,33 +1111,37 @@
           <t>left</t>
         </is>
       </c>
-      <c r="M9" t="n">
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
         <v>4</v>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="n">
-        <v>1.2</v>
-      </c>
       <c r="Q9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R9" t="n">
         <v>0.2</v>
       </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1172,65 +1166,57 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_33.jpg</t>
-        </is>
-      </c>
+          <t>stimuli/bread/bread_18.jpg</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>2</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
-      <c r="O10" t="n">
-        <v>3</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4</v>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R10" t="n">
         <v>0.2</v>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
         <v>7</v>
       </c>
       <c r="T10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1250,40 +1236,54 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_19.jpg</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_28.jpg</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
-        </is>
-      </c>
       <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
-      </c>
-      <c r="N11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
       <c r="O11" t="inlineStr"/>
-      <c r="P11" t="n">
-        <v>2</v>
-      </c>
+      <c r="P11" t="inlineStr"/>
       <c r="Q11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R11" t="inlineStr"/>
+        <v>1.2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.2</v>
+      </c>
       <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="n">
         <v>6</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1291,7 +1291,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1311,54 +1311,40 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_15.jpg</t>
+          <t>stimuli/bread/bread_18.jpg</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="M12" t="n">
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="n">
         <v>4</v>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>5</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -1366,7 +1352,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1386,7 +1372,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_12.jpg</t>
+          <t>stimuli/hand/hand_18.jpg</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1395,28 +1381,42 @@
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
       <c r="O13" t="inlineStr"/>
-      <c r="P13" t="n">
-        <v>2</v>
-      </c>
+      <c r="P13" t="inlineStr"/>
       <c r="Q13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R13" t="inlineStr"/>
+        <v>1.2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.2</v>
+      </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T13" t="n">
         <v>10</v>
@@ -1447,70 +1447,70 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/hammer/hammer_12.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_15.jpg</t>
+          <t>stimuli/flower/flower_28.jpg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/hammer/hammer_12.jpg</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_15.jpg</t>
+          <t>stimuli/flower/flower_28.jpg</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="M14" t="n">
-        <v>2</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>inside</t>
-        </is>
-      </c>
-      <c r="O14" t="n">
+          <t>right</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="n">
         <v>3</v>
       </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
       <c r="P14" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q14" t="n">
         <v>1.5</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>0.2</v>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T14" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1530,23 +1530,27 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>stimuli/ball/ball_33.jpg</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
           <t>stimuli/house/house_02.jpg</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_18.jpg</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>stimuli/dog/dog_15.jpg</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/house/house_02.jpg</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/dog/dog_15.jpg</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1559,33 +1563,37 @@
           <t>left</t>
         </is>
       </c>
-      <c r="M15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="n">
+        <v>2</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
       <c r="P15" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="Q15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R15" t="n">
         <v>0.2</v>
       </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
       <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
         <v>9</v>
       </c>
-      <c r="T15" t="n">
-        <v>3</v>
-      </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1605,70 +1613,62 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_28.jpg</t>
-        </is>
-      </c>
+          <t>stimuli/jacket/jacket_19.jpg</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_28.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
-      <c r="O16" t="n">
-        <v>5</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.5</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>4</v>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
       <c r="Q16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R16" t="n">
         <v>0.2</v>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="U16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1688,70 +1688,48 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_18.jpg</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
           <t>stimuli/dog/dog_15.jpg</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_18.jpg</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_15.jpg</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
-      <c r="O17" t="n">
-        <v>6</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.5</v>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="n">
+        <v>4</v>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
       <c r="Q17" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R17" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.5</v>
+      </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1771,23 +1749,27 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_19.jpg</t>
+          <t>stimuli/hand/hand_18.jpg</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>stimuli/bread/bread_18.jpg</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>stimuli/hammer/hammer_12.jpg</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/bread/bread_18.jpg</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/hammer/hammer_12.jpg</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1800,33 +1782,37 @@
           <t>left</t>
         </is>
       </c>
-      <c r="M18" t="n">
-        <v>2</v>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
       <c r="P18" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R18" t="n">
         <v>0.2</v>
       </c>
-      <c r="R18" t="n">
-        <v>1</v>
-      </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1846,27 +1832,23 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>stimuli/dog/dog_15.jpg</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_28.jpg</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_21.jpg</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_12.jpg</t>
-        </is>
-      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_12.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1880,31 +1862,27 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>inside</t>
-        </is>
-      </c>
-      <c r="O19" t="n">
-        <v>3</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2</v>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
       <c r="Q19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R19" t="n">
         <v>0.2</v>
       </c>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="n">
         <v>6</v>
       </c>
-      <c r="T19" t="n">
-        <v>4</v>
-      </c>
       <c r="U19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1929,12 +1907,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>stimuli/house/house_02.jpg</t>
+          <t>stimuli/hammer/hammer_12.jpg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -1950,33 +1928,33 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="n">
         <v>3</v>
       </c>
-      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
-      <c r="P20" t="n">
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>0.2</v>
       </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -1984,7 +1962,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2004,7 +1982,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/bicycle/bicycle_39.jpg</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2012,40 +1990,62 @@
           <t>stimuli/dog/dog_15.jpg</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>stimuli/hand/hand_18.jpg</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>stimuli/dog/dog_15.jpg</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stimuli/hand/hand_18.jpg</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M21" t="n">
+          <t>left</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
         <v>4</v>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="n">
-        <v>2</v>
-      </c>
       <c r="Q21" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R21" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.2</v>
+      </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T21" t="n">
         <v>5</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_12.jpg</t>
+          <t>stimuli/house/house_02.jpg</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2073,54 +2073,62 @@
           <t>stimuli/flower/flower_28.jpg</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>stimuli/jacket/jacket_19.jpg</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/flower/flower_28.jpg</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/jacket/jacket_19.jpg</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="M22" t="n">
-        <v>1</v>
-      </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="n">
+        <v>4</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
       <c r="P22" t="n">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="Q22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R22" t="n">
         <v>0.2</v>
       </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T22" t="n">
         <v>6</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2140,40 +2148,54 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>stimuli/bicycle/bicycle_39.jpg</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>stimuli/hammer/hammer_12.jpg</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>2</v>
-      </c>
-      <c r="N23" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
+      </c>
       <c r="O23" t="inlineStr"/>
-      <c r="P23" t="n">
-        <v>2</v>
-      </c>
+      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R23" t="inlineStr"/>
+        <v>1.2</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.2</v>
+      </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -2181,7 +2203,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2201,70 +2223,62 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_18.jpg</t>
+          <t>stimuli/ball/ball_33.jpg</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_19.jpg</t>
-        </is>
-      </c>
+          <t>stimuli/hand/hand_18.jpg</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_19.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
-      <c r="O24" t="n">
-        <v>6</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.5</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
       <c r="Q24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R24" t="n">
         <v>0.2</v>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="U24" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2284,62 +2298,70 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/bicycle/bicycle_39.jpg</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+          <t>stimuli/chair/chair_21.jpg</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>stimuli/flower/flower_28.jpg</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/flower/flower_28.jpg</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="n">
+        <v>3</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
       <c r="P25" t="n">
-        <v>1.2</v>
+        <v>7</v>
       </c>
       <c r="Q25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R25" t="n">
         <v>0.2</v>
       </c>
-      <c r="R25" t="n">
-        <v>1</v>
-      </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2359,70 +2381,48 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_18.jpg</t>
+          <t>stimuli/hammer/hammer_12.jpg</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_12.jpg</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_12.jpg</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
+          <t>stimuli/hand/hand_18.jpg</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="M26" t="n">
-        <v>4</v>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
-      <c r="O26" t="n">
-        <v>6</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.5</v>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="n">
+        <v>2</v>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
       <c r="Q26" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R26" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.5</v>
+      </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T26" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="U26" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2447,52 +2447,60 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>stimuli/dog/dog_15.jpg</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>stimuli/house/house_02.jpg</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/dog/dog_15.jpg</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/house/house_02.jpg</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="M27" t="n">
-        <v>3</v>
-      </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="n">
+        <v>2</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
       <c r="P27" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="Q27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R27" t="n">
         <v>0.2</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>6</v>
       </c>
       <c r="T27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28">
@@ -2517,65 +2525,65 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_33.jpg</t>
+          <t>stimuli/hammer/hammer_12.jpg</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_12.jpg</t>
+          <t>stimuli/bread/bread_18.jpg</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>stimuli/house/house_02.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_12.jpg</t>
+          <t>stimuli/bread/bread_18.jpg</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>stimuli/house/house_02.jpg</t>
+          <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="M28" t="n">
-        <v>2</v>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>inside</t>
-        </is>
-      </c>
-      <c r="O28" t="n">
+          <t>left</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="n">
+        <v>4</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S28" t="n">
+        <v>7</v>
+      </c>
+      <c r="T28" t="n">
         <v>3</v>
       </c>
-      <c r="P28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="n">
-        <v>1</v>
-      </c>
-      <c r="T28" t="n">
-        <v>7</v>
-      </c>
       <c r="U28" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -2600,12 +2608,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_39.jpg</t>
+          <t>stimuli/hand/hand_18.jpg</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_15.jpg</t>
+          <t>stimuli/flower/flower_28.jpg</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
@@ -2621,33 +2629,33 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
       <c r="O29" t="inlineStr"/>
-      <c r="P29" t="n">
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>0.2</v>
       </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
       <c r="S29" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -2675,12 +2683,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_18.jpg</t>
+          <t>stimuli/house/house_02.jpg</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_19.jpg</t>
+          <t>stimuli/bread/bread_18.jpg</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -2692,23 +2700,23 @@
           <t>2</t>
         </is>
       </c>
-      <c r="M30" t="n">
-        <v>1</v>
-      </c>
-      <c r="N30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="n">
+        <v>1</v>
+      </c>
       <c r="O30" t="inlineStr"/>
-      <c r="P30" t="n">
-        <v>2</v>
-      </c>
+      <c r="P30" t="inlineStr"/>
       <c r="Q30" t="n">
+        <v>2</v>
+      </c>
+      <c r="R30" t="n">
         <v>0.5</v>
       </c>
-      <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T30" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -2716,7 +2724,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -2736,65 +2744,57 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_12.jpg</t>
+          <t>stimuli/flower/flower_28.jpg</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_18.jpg</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
           <t>stimuli/chair/chair_21.jpg</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_18.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_21.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>3</v>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S31" t="n">
+        <v>6</v>
+      </c>
+      <c r="T31" t="n">
         <v>4</v>
       </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
-      <c r="O31" t="n">
-        <v>5</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="n">
-        <v>7</v>
-      </c>
-      <c r="T31" t="n">
-        <v>3</v>
-      </c>
       <c r="U31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
